--- a/2_Formulas_Functions/8_Text_Functions.xlsx
+++ b/2_Formulas_Functions/8_Text_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1 Visual Studio Code\Personal\DOA\1_Excel_DOA_Course\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDE4963-8F7E-4211-878F-EF3E693A101E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B951359-0C82-4DBB-BE5F-8C2D3F1D7E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" r:id="rId1"/>
@@ -473,7 +473,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -601,11 +601,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -625,10 +681,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2026,16 +2086,16 @@
       <c r="O1" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19" t="s">
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -4805,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="str">
-        <f t="shared" si="1"/>
+        <f>RIGHT(A20,7)</f>
         <v>0123566</v>
       </c>
     </row>
@@ -4894,11 +4954,11 @@
       <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -5673,7 +5733,8 @@
   <dimension ref="A2:BX25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:76" x14ac:dyDescent="0.3">
@@ -5684,7 +5745,7 @@
     </row>
     <row r="3" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
-        <f>_xlfn.TEXTJOIN(", ",FALSE,Data!H2:H21)</f>
+        <f>_xlfn.TEXTJOIN(", ",TRUE,Data!H2:H21)</f>
         <v>Kafka, DataBricks, Spark, Python, GCP, Power BI, GCP, Airflow, Hadoop, R, Azure, Java, SQL, DataBricks, Kafka, DataBricks, Spark, Python, GCP, DataBricks, Hadoop, Java, Snowflake, Airflow, DataBricks, Azure, Java, SQL, DataBricks, Snowflake, Airflow, DataBricks, Scala, Azure, R, Kafka, Snowflake, Excel, Scala, Excel, Power BI, R, Scala, R, Hadoop, Power BI, SQL, Snowflake, Airflow, DataBricks, Java, Scala, R, DataBricks, Azure, Scala, Power BI, GCP, Airflow, Hadoop, R, DataBricks, Hadoop, Java, Snowflake, Power BI, Tableau, Airflow, SQL, DataBricks, Hadoop, Java, DataBricks, Hadoop, Java</v>
       </c>
     </row>
@@ -5695,402 +5756,400 @@
       <c r="B5" s="16"/>
     </row>
     <row r="6" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="M6" s="20" t="s">
+      <c r="M6" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="N6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="O6" s="20" t="s">
+      <c r="O6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="P6" s="20" t="s">
+      <c r="P6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="Q6" s="20" t="s">
+      <c r="Q6" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="R6" s="20" t="s">
+      <c r="R6" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="S6" s="20" t="s">
+      <c r="S6" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="T6" s="20" t="s">
+      <c r="T6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="U6" s="20" t="s">
+      <c r="U6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="V6" s="20" t="s">
+      <c r="V6" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="W6" s="20" t="s">
+      <c r="W6" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="X6" s="20" t="s">
+      <c r="X6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="Y6" s="20" t="s">
+      <c r="Y6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="Z6" s="20" t="s">
+      <c r="Z6" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="AA6" s="20" t="s">
+      <c r="AA6" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="AB6" s="20" t="s">
+      <c r="AB6" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="AC6" s="20" t="s">
+      <c r="AC6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="AD6" s="20" t="s">
+      <c r="AD6" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="AE6" s="20" t="s">
+      <c r="AE6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="AF6" s="20" t="s">
+      <c r="AF6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="AG6" s="20" t="s">
+      <c r="AG6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="AH6" s="20" t="s">
+      <c r="AH6" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="AI6" s="20" t="s">
+      <c r="AI6" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="AJ6" s="20" t="s">
+      <c r="AJ6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="AK6" s="20" t="s">
+      <c r="AK6" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="AL6" s="20" t="s">
+      <c r="AL6" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="AM6" s="20" t="s">
+      <c r="AM6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="AN6" s="20" t="s">
+      <c r="AN6" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="AO6" s="20" t="s">
+      <c r="AO6" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="AP6" s="20" t="s">
+      <c r="AP6" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="AQ6" s="20" t="s">
+      <c r="AQ6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="AR6" s="20" t="s">
+      <c r="AR6" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="AS6" s="20" t="s">
+      <c r="AS6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="AT6" s="20" t="s">
+      <c r="AT6" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="AU6" s="20" t="s">
+      <c r="AU6" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="AV6" s="20" t="s">
+      <c r="AV6" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="AW6" s="20" t="s">
+      <c r="AW6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="AX6" s="20" t="s">
+      <c r="AX6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="AY6" s="20" t="s">
+      <c r="AY6" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="AZ6" s="20" t="s">
+      <c r="AZ6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BA6" s="20" t="s">
+      <c r="BA6" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BB6" s="20" t="s">
+      <c r="BB6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="BC6" s="20" t="s">
+      <c r="BC6" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BD6" s="20" t="s">
+      <c r="BD6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BE6" s="20" t="s">
+      <c r="BE6" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BF6" s="20" t="s">
+      <c r="BF6" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="BG6" s="20" t="s">
+      <c r="BG6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BH6" s="20" t="s">
+      <c r="BH6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BI6" s="20" t="s">
+      <c r="BI6" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BJ6" s="20" t="s">
+      <c r="BJ6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="BK6" s="20" t="s">
+      <c r="BK6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BL6" s="20" t="s">
+      <c r="BL6" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BM6" s="20" t="s">
+      <c r="BM6" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="BN6" s="20" t="s">
+      <c r="BN6" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BO6" s="20" t="s">
+      <c r="BO6" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="BP6" s="20" t="s">
+      <c r="BP6" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BQ6" s="20" t="s">
+      <c r="BQ6" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="BR6" s="20" t="s">
+      <c r="BR6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="BS6" s="20" t="s">
+      <c r="BS6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BT6" s="20" t="s">
+      <c r="BT6" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BU6" s="20" t="s">
+      <c r="BU6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="BV6" s="20" t="s">
+      <c r="BV6" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BW6" s="20" t="s">
+      <c r="BW6" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BX6" s="20"/>
-    </row>
-    <row r="8" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="BX6" s="19"/>
+    </row>
+    <row r="7" spans="1:76" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:76" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="str" cm="1">
+      <c r="A9" s="22" t="str" cm="1">
         <f t="array" ref="A9:A25">_xlfn.UNIQUE(TRANSPOSE(6:6))</f>
         <v>Kafka</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="23">
         <f>COUNTIF($6:$6,A9)</f>
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="str">
+      <c r="A10" s="5" t="str">
         <v>DataBricks</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="6">
         <f t="shared" ref="B10:B25" si="0">COUNTIF($6:$6,A10)</f>
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="str">
+      <c r="A11" s="5" t="str">
         <v>Spark</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="str">
+      <c r="A12" s="5" t="str">
         <v>Python</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="str">
+      <c r="A13" s="5" t="str">
         <v>GCP</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="str">
+      <c r="A14" s="5" t="str">
         <v>Power BI</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="str">
+      <c r="A15" s="5" t="str">
         <v>Airflow</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:76" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="str">
+      <c r="A16" s="5" t="str">
         <v>Hadoop</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="str">
+      <c r="A17" s="5" t="str">
         <v>R</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="str">
+      <c r="A18" s="5" t="str">
         <v>Azure</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="str">
+      <c r="A19" s="5" t="str">
         <v>Java</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="str">
+      <c r="A20" s="5" t="str">
         <v>SQL</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="str">
+      <c r="A21" s="5" t="str">
         <v>Snowflake</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="str">
+      <c r="A22" s="5" t="str">
         <v>Scala</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="str">
+      <c r="A23" s="5" t="str">
         <v>Excel</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="str">
+      <c r="A24" s="5" t="str">
         <v>Tableau</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="24">
         <v>0</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
